--- a/product_selector_out/STM32F101.xlsx
+++ b/product_selector_out/STM32F101.xlsx
@@ -1421,74 +1421,74 @@
       </c>
       <c r="U13" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V13" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA13" s="4" t="inlineStr">
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD13" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH13" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD13" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AE13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG13" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH13" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI13" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="AL13" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM13" s="4" t="inlineStr">
@@ -1748,74 +1748,74 @@
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA14" s="4" t="inlineStr">
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD14" s="4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AE14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH14" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD14" s="4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AE14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG14" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH14" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI14" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AL14" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM14" s="4" t="inlineStr">
@@ -2075,74 +2075,74 @@
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V15" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="inlineStr">
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD15" s="4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AE15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH15" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD15" s="4" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="AE15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG15" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH15" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI15" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="AL15" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM15" s="4" t="inlineStr">
@@ -2402,74 +2402,74 @@
       </c>
       <c r="U16" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V16" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA16" s="4" t="inlineStr">
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD16" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AE16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH16" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD16" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AE16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG16" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH16" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI16" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="AL16" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM16" s="4" t="inlineStr">
@@ -2729,74 +2729,74 @@
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V17" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA17" s="4" t="inlineStr">
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD17" s="4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AE17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH17" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD17" s="4" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="AE17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG17" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH17" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI17" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="AL17" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM17" s="4" t="inlineStr">
@@ -3383,74 +3383,74 @@
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="W19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V19" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="W19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Y19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Z19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AA19" s="4" t="inlineStr">
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD19" s="4" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AE19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH19" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AC19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD19" s="4" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="AE19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AF19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AG19" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AH19" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AI19" s="4" t="inlineStr">
         <is>
           <t>-</t>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="AL19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM19" s="4" t="inlineStr">
@@ -11266,9 +11266,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL12" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
@@ -11508,14 +11508,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
@@ -11538,9 +11538,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="9" t="inlineStr">
@@ -11593,9 +11593,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -11835,14 +11835,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
@@ -11865,9 +11865,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="9" t="inlineStr">
@@ -11920,9 +11920,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -12162,14 +12162,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
@@ -12192,9 +12192,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="9" t="inlineStr">
@@ -12247,9 +12247,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -12489,14 +12489,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
@@ -12519,9 +12519,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="9" t="inlineStr">
@@ -12574,9 +12574,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -12816,14 +12816,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
@@ -12846,9 +12846,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="9" t="inlineStr">
@@ -12901,9 +12901,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL17" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="6" t="inlineStr">
@@ -13228,9 +13228,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="9" t="inlineStr">
@@ -13470,14 +13470,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="U19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="V19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
@@ -13500,9 +13500,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="9" t="inlineStr">
@@ -13555,9 +13555,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -13882,9 +13882,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="9" t="inlineStr">
@@ -14209,9 +14209,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="9" t="inlineStr">
@@ -14536,9 +14536,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="9" t="inlineStr">
@@ -14863,9 +14863,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="9" t="inlineStr">
@@ -15190,9 +15190,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="9" t="inlineStr">
@@ -16171,9 +16171,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL27" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL27" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM27" s="9" t="inlineStr">
@@ -16498,9 +16498,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL28" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM28" s="9" t="inlineStr">
@@ -17479,9 +17479,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL31" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM31" s="9" t="inlineStr">
@@ -17806,9 +17806,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL32" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL32" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM32" s="9" t="inlineStr">
@@ -18133,9 +18133,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL33" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL33" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM33" s="9" t="inlineStr">
@@ -19768,9 +19768,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL38" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL38" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM38" s="9" t="inlineStr">
@@ -20095,9 +20095,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL39" s="8" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL39" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM39" s="9" t="inlineStr">

--- a/product_selector_out/STM32F101.xlsx
+++ b/product_selector_out/STM32F101.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM40"/>
+  <dimension ref="A1:BN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.52734375" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rf.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c4.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101c8.pdf</t>
         </is>
       </c>
@@ -10470,12 +10617,17 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f101rc.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -10496,16 +10648,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -10518,6 +10668,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -10537,7 +10688,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -10583,7 +10736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM40"/>
+  <dimension ref="A1:BN40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -10651,6 +10804,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10984,6 +11138,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -11079,6 +11238,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -11401,7 +11561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11728,7 +11893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12055,7 +12225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12382,7 +12557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12709,7 +12889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13036,7 +13221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13363,7 +13553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13690,7 +13885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14017,7 +14217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14344,7 +14549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14671,7 +14881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14998,7 +15213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15325,7 +15545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15652,7 +15877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15979,7 +16209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16306,7 +16541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16633,7 +16873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16960,7 +17205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17287,7 +17537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17614,7 +17869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17941,7 +18201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18268,7 +18533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18595,7 +18865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18922,7 +19197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19249,7 +19529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19576,7 +19861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19903,7 +20193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20230,7 +20525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20557,7 +20857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20565,8 +20870,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
